--- a/test_files/BTG_P.INMOBILIARIO_EEFF_2025-06-30.xlsx
+++ b/test_files/BTG_P.INMOBILIARIO_EEFF_2025-06-30.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDriveUniversidad EIA\Documentos\Valen\BTG Pactual\Proyectos\iastronauts_creditiq\test_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABAE9BF-3EF9-4FEF-8240-E62DB9E83656}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CCD782-CB34-4A8D-A984-110C1CE9F0EA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7485" firstSheet="15" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7485" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BALANCE" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>Concepto</t>
   </si>
@@ -81,9 +81,6 @@
     <t>Utilidad del período</t>
   </si>
   <si>
-    <t>Total activo neto</t>
-  </si>
-  <si>
     <t>Jun2025 Acum</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
     <t>Gastos operacionales</t>
   </si>
   <si>
-    <t>Utilidad operación</t>
-  </si>
-  <si>
     <t>Gastos administrativos</t>
   </si>
   <si>
@@ -117,21 +111,12 @@
     <t>Jun2024</t>
   </si>
   <si>
-    <t>Saldo inicial</t>
-  </si>
-  <si>
     <t>Aportes</t>
   </si>
   <si>
     <t>Retiros</t>
   </si>
   <si>
-    <t>Utilidad</t>
-  </si>
-  <si>
-    <t>Saldo final</t>
-  </si>
-  <si>
     <t>Valorización inversiones</t>
   </si>
   <si>
@@ -153,12 +138,6 @@
     <t>Flujo operación</t>
   </si>
   <si>
-    <t>Obligaciones</t>
-  </si>
-  <si>
-    <t>Flujo financiación</t>
-  </si>
-  <si>
     <t>Disminución efectivo</t>
   </si>
   <si>
@@ -309,18 +288,6 @@
     <t>BTG Pactual Fondo Liquidez</t>
   </si>
   <si>
-    <t>Inverlink Rentas</t>
-  </si>
-  <si>
-    <t>Future</t>
-  </si>
-  <si>
-    <t>Cedi Sibaté</t>
-  </si>
-  <si>
-    <t>Proyecto Calle 93</t>
-  </si>
-  <si>
     <t>Acum2025</t>
   </si>
   <si>
@@ -367,13 +334,137 @@
   </si>
   <si>
     <t>Instrumentos financieros</t>
+  </si>
+  <si>
+    <t>Activos netos de los inversionistas</t>
+  </si>
+  <si>
+    <t>Total activo neto de los inversionistas</t>
+  </si>
+  <si>
+    <t>Total pasivo y activos netos de los inversionistas</t>
+  </si>
+  <si>
+    <t>Utilidad por actividades de operación</t>
+  </si>
+  <si>
+    <t>Resultado integral del periodo</t>
+  </si>
+  <si>
+    <t>Activos netos de los inversionistas al 31 de diciembre</t>
+  </si>
+  <si>
+    <t>Aportes de los inversionistas</t>
+  </si>
+  <si>
+    <t>Retiros de los inversionitas</t>
+  </si>
+  <si>
+    <t>Utilidad del periodo</t>
+  </si>
+  <si>
+    <t>Activos netos de los inversionistas al final del periodo</t>
+  </si>
+  <si>
+    <t>Flujo de efectivo de actividades de operación</t>
+  </si>
+  <si>
+    <t>utilidad del periodo</t>
+  </si>
+  <si>
+    <t>Conciliacion entre la utilidad del periodo y el efectivo neto usado en las actividades de operación</t>
+  </si>
+  <si>
+    <t>Cambio neto en activos y pasivos operacionales</t>
+  </si>
+  <si>
+    <t>Flujo de efectivo de actividades de financiacion</t>
+  </si>
+  <si>
+    <t>Disminucion de obligaciones financieras</t>
+  </si>
+  <si>
+    <t>Efectivo neto (usado en) provisto por actividades de financiacion</t>
+  </si>
+  <si>
+    <t>Efectivo al comienzo del periodo</t>
+  </si>
+  <si>
+    <t>Efectivo al final del periodo</t>
+  </si>
+  <si>
+    <t>Instrumentos de Patrimonio</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>Inversiones Derechos Fiduciarios</t>
+  </si>
+  <si>
+    <t>Fideicomiso Inverlink Rentas</t>
+  </si>
+  <si>
+    <t>Fideicomiso Future</t>
+  </si>
+  <si>
+    <t>Fideicomiso La Cofradía</t>
+  </si>
+  <si>
+    <t>Fideicomiso PA Atlas</t>
+  </si>
+  <si>
+    <t>Fideicomiso DZF Fondo BTG</t>
+  </si>
+  <si>
+    <t>Fideicomiso Cedis La 14</t>
+  </si>
+  <si>
+    <t>Fideicomiso Cedi Sibaté</t>
+  </si>
+  <si>
+    <t>Fideicomiso Proyecto Calle 93</t>
+  </si>
+  <si>
+    <t>Fideicomiso Tocancipá</t>
+  </si>
+  <si>
+    <t>Fideicomiso Student Living Calle 18</t>
+  </si>
+  <si>
+    <t>Fideicomiso Arriendos y Concesiones Ofi</t>
+  </si>
+  <si>
+    <t>Fideicomiso oficinas tranvia plaza</t>
+  </si>
+  <si>
+    <t>Fideicomiso Student Living Calle 21</t>
+  </si>
+  <si>
+    <t>Fideicomiso ofi 7 II</t>
+  </si>
+  <si>
+    <t>Fideicomiso Oficinas 14x97</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,13 +490,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -706,21 +803,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -728,10 +825,10 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>727577</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>1168949</v>
       </c>
     </row>
@@ -739,10 +836,10 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1540301590</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1580453555</v>
       </c>
     </row>
@@ -750,10 +847,10 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>939619</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1228915</v>
       </c>
     </row>
@@ -761,10 +858,10 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>7055577</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>7283183</v>
       </c>
     </row>
@@ -772,10 +869,10 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>1549024363</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1590134602</v>
       </c>
     </row>
@@ -783,10 +880,10 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>190889</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>169371</v>
       </c>
     </row>
@@ -794,10 +891,10 @@
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>290590422</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>291129457</v>
       </c>
     </row>
@@ -805,10 +902,10 @@
       <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>22371047</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>66821591</v>
       </c>
     </row>
@@ -816,44 +913,60 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>313152358</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>358120419</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>1179299264</v>
-      </c>
-      <c r="C11">
-        <v>1128907570</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>56572741</v>
-      </c>
-      <c r="C12">
-        <v>103106613</v>
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1179299264</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1128907570</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>56572741</v>
+      </c>
+      <c r="C13" s="1">
+        <v>103106613</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="1">
         <v>1235872005</v>
       </c>
-      <c r="C13">
+      <c r="C14" s="1">
         <v>1232014183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1549024363</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1590134602</v>
       </c>
     </row>
   </sheetData>
@@ -875,15 +988,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>84040319</v>
@@ -894,7 +1007,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>1456261271</v>
@@ -905,7 +1018,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>1540301590</v>
@@ -926,24 +1039,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B2">
         <v>12.68</v>
@@ -960,7 +1073,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>12.11</v>
@@ -990,15 +1103,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B2">
         <v>84040319</v>
@@ -1009,7 +1122,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>43408</v>
@@ -1020,7 +1133,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <v>112337</v>
@@ -1044,15 +1157,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>6000000</v>
@@ -1063,7 +1176,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>5326631</v>
@@ -1074,7 +1187,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B4">
         <v>2559696</v>
@@ -1085,7 +1198,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>2042000</v>
@@ -1096,7 +1209,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>2040000</v>
@@ -1107,7 +1220,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>1400000</v>
@@ -1118,7 +1231,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B8">
         <v>850000</v>
@@ -1129,7 +1242,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B9">
         <v>780000</v>
@@ -1140,7 +1253,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B10">
         <v>720000</v>
@@ -1151,7 +1264,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B11">
         <v>350000</v>
@@ -1162,7 +1275,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B12">
         <v>302720</v>
@@ -1173,7 +1286,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1189,128 +1302,241 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" t="s">
-        <v>88</v>
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2">
-        <v>84040319</v>
-      </c>
-      <c r="C2">
-        <v>116317145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3">
-        <v>280284603</v>
-      </c>
-      <c r="C3">
-        <v>295427437</v>
+        <v>82</v>
+      </c>
+      <c r="B3" s="1">
+        <v>84040319</v>
+      </c>
+      <c r="C3" s="1">
+        <v>116317145</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4">
-        <v>187904571</v>
-      </c>
-      <c r="C4">
-        <v>185043748</v>
+        <v>119</v>
+      </c>
+      <c r="B4" s="1">
+        <v>84040319</v>
+      </c>
+      <c r="C4" s="1">
+        <v>116317145</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5">
-        <v>180276702</v>
-      </c>
-      <c r="C5">
-        <v>179982026</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6">
-        <v>162209143</v>
-      </c>
-      <c r="C6">
-        <v>165218294</v>
+        <v>121</v>
+      </c>
+      <c r="B6" s="1">
+        <v>280284603</v>
+      </c>
+      <c r="C6" s="1">
+        <v>295427437</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7">
-        <v>105261865</v>
-      </c>
-      <c r="C7">
-        <v>104540076</v>
+        <v>122</v>
+      </c>
+      <c r="B7" s="1">
+        <v>187904571</v>
+      </c>
+      <c r="C7" s="1">
+        <v>185043748</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8">
-        <v>96931417</v>
-      </c>
-      <c r="C8">
-        <v>95403458</v>
+        <v>123</v>
+      </c>
+      <c r="B8" s="1">
+        <v>180276702</v>
+      </c>
+      <c r="C8" s="1">
+        <v>179982026</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9">
-        <v>82733205</v>
-      </c>
-      <c r="C9">
-        <v>85130582</v>
+        <v>124</v>
+      </c>
+      <c r="B9" s="1">
+        <v>162209143</v>
+      </c>
+      <c r="C9" s="1">
+        <v>165218294</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10">
-        <v>81219030</v>
-      </c>
-      <c r="C10">
-        <v>81180294</v>
+        <v>125</v>
+      </c>
+      <c r="B10" s="1">
+        <v>105261865</v>
+      </c>
+      <c r="C10" s="1">
+        <v>104540076</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11">
+        <v>126</v>
+      </c>
+      <c r="B11" s="1">
+        <v>96931417</v>
+      </c>
+      <c r="C11" s="1">
+        <v>95403458</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="1">
+        <v>82733205</v>
+      </c>
+      <c r="C12" s="1">
+        <v>85130582</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="1">
+        <v>81219030</v>
+      </c>
+      <c r="C13" s="1">
+        <v>81180294</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="1">
         <v>59291390</v>
       </c>
-      <c r="C11">
+      <c r="C14" s="1">
         <v>54796909</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="1">
+        <v>55769181</v>
+      </c>
+      <c r="C15" s="1">
+        <v>55308117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="1">
+        <v>39641535</v>
+      </c>
+      <c r="C16" s="1">
+        <v>39522407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="1">
+        <v>37064363</v>
+      </c>
+      <c r="C17" s="1">
+        <v>32246827</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="1">
+        <v>33764804</v>
+      </c>
+      <c r="C18" s="1">
+        <v>32179965</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="1">
+        <v>28128464</v>
+      </c>
+      <c r="C19" s="1">
+        <v>29037664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="1">
+        <v>25690998</v>
+      </c>
+      <c r="C20" s="1">
+        <v>26118606</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1456261271</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1464136410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1540301590</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1580453555</v>
       </c>
     </row>
   </sheetData>
@@ -1328,21 +1554,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
         <v>17</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B2">
         <v>79761719</v>
@@ -1359,7 +1585,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B3">
         <v>5117909</v>
@@ -1376,7 +1602,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B4">
         <v>33636</v>
@@ -1393,7 +1619,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B5">
         <v>17371</v>
@@ -1410,7 +1636,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1440,12 +1666,12 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>16493357</v>
@@ -1453,7 +1679,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>8761811</v>
@@ -1461,7 +1687,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B4">
         <v>2385</v>
@@ -1482,15 +1708,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>1137935</v>
@@ -1501,7 +1727,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>762171</v>
@@ -1512,7 +1738,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>455294</v>
@@ -1523,7 +1749,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>300221</v>
@@ -1534,7 +1760,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B6">
         <v>134526</v>
@@ -1545,7 +1771,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B7">
         <v>94452</v>
@@ -1569,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,7 +1820,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B3">
         <v>1540301590</v>
@@ -1622,7 +1848,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>7055577</v>
@@ -1641,29 +1867,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>17</v>
-      </c>
-      <c r="E1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2">
         <v>84930635</v>
@@ -1680,7 +1912,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>-25257553</v>
@@ -1697,7 +1929,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="B4">
         <v>59673082</v>
@@ -1714,7 +1946,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>-3100341</v>
@@ -1731,7 +1963,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>56572741</v>
@@ -1743,6 +1975,23 @@
         <v>29085096</v>
       </c>
       <c r="E6">
+        <v>29021052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7">
+        <v>56572741</v>
+      </c>
+      <c r="C7">
+        <v>67222111</v>
+      </c>
+      <c r="D7">
+        <v>29085096</v>
+      </c>
+      <c r="E7">
         <v>29021052</v>
       </c>
     </row>
@@ -1755,21 +2004,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="B2">
         <v>1232014183</v>
@@ -1780,7 +2033,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="B3">
         <v>405476</v>
@@ -1791,7 +2044,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="B4">
         <v>-53120395</v>
@@ -1802,7 +2055,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="B5">
         <v>56572741</v>
@@ -1813,7 +2066,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="B6">
         <v>1235872005</v>
@@ -1829,183 +2082,229 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="49.7109375" customWidth="1"/>
+    <col min="2" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2">
-        <v>56572741</v>
-      </c>
-      <c r="C2">
-        <v>67222111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>3643902</v>
-      </c>
-      <c r="C3">
-        <v>-48843552</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>5598841</v>
-      </c>
-      <c r="C4">
-        <v>6598295</v>
+        <v>110</v>
+      </c>
+      <c r="B3" s="1">
+        <v>56572741</v>
+      </c>
+      <c r="C3" s="1">
+        <v>67222111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>36508063</v>
-      </c>
-      <c r="C5">
-        <v>-38463850</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3643902</v>
+      </c>
+      <c r="C5" s="1">
+        <v>-48843552</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>289296</v>
-      </c>
-      <c r="C6">
-        <v>6781</v>
+        <v>27</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5598841</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6598295</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7">
-        <v>227606</v>
-      </c>
-      <c r="C7">
-        <v>235921</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>21518</v>
-      </c>
-      <c r="C8">
-        <v>-109097</v>
+        <v>28</v>
+      </c>
+      <c r="B8" s="1">
+        <v>36508063</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-38463850</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9">
-        <v>-44450544</v>
-      </c>
-      <c r="C9">
-        <v>-15217593</v>
+        <v>5</v>
+      </c>
+      <c r="B9" s="1">
+        <v>289296</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6781</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10">
-        <v>-6137559</v>
-      </c>
-      <c r="C10">
-        <v>-6562718</v>
+        <v>29</v>
+      </c>
+      <c r="B10" s="1">
+        <v>227606</v>
+      </c>
+      <c r="C10" s="1">
+        <v>235921</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11">
-        <v>52273864</v>
-      </c>
-      <c r="C11">
-        <v>-35133702</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>21518</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-109097</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>405476</v>
-      </c>
-      <c r="C12">
-        <v>10730949</v>
+        <v>30</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-44450544</v>
+      </c>
+      <c r="C12" s="1">
+        <v>-15217593</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>-53120395</v>
-      </c>
-      <c r="C13">
-        <v>-27650943</v>
+        <v>31</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-6137559</v>
+      </c>
+      <c r="C13" s="1">
+        <v>-6562718</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14">
-        <v>-317</v>
-      </c>
-      <c r="C14">
-        <v>-2155</v>
+        <v>32</v>
+      </c>
+      <c r="B14" s="1">
+        <v>52273864</v>
+      </c>
+      <c r="C14" s="1">
+        <v>-35133702</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15">
-        <v>-52715236</v>
-      </c>
-      <c r="C15">
-        <v>-16922149</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1">
+        <v>405476</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10730949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-53120395</v>
+      </c>
+      <c r="C17" s="1">
+        <v>-27650943</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="1">
+        <v>-317</v>
+      </c>
+      <c r="C18" s="1">
+        <v>-2155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="1">
+        <v>-52715236</v>
+      </c>
+      <c r="C19" s="1">
+        <v>-16922149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="1">
         <v>-441372</v>
       </c>
-      <c r="C16">
+      <c r="C20" s="1">
         <v>-52055851</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1186949</v>
+      </c>
+      <c r="C21" s="1">
+        <v>56514173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="1">
+        <v>727577</v>
+      </c>
+      <c r="C22" s="1">
+        <v>4458322</v>
       </c>
     </row>
   </sheetData>
@@ -2020,18 +2319,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>408532</v>
@@ -2042,7 +2341,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>310501</v>
@@ -2053,7 +2352,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>5608</v>
@@ -2064,7 +2363,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>2936</v>
@@ -2088,15 +2387,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>577648</v>
@@ -2107,7 +2406,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B3">
         <v>361971</v>
@@ -2131,15 +2430,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B2">
         <v>5526488</v>
@@ -2150,7 +2449,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>1408448</v>
@@ -2161,7 +2460,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>75000</v>
@@ -2172,7 +2471,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>45641</v>
@@ -2196,15 +2495,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>112337</v>
@@ -2215,7 +2514,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>43408</v>
@@ -2226,7 +2525,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>24567</v>
@@ -2237,7 +2536,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>10577</v>
@@ -2261,15 +2560,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B2">
         <v>200000000</v>
@@ -2280,7 +2579,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>64991581</v>
@@ -2291,7 +2590,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <v>20000000</v>
@@ -2302,7 +2601,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B5">
         <v>5406417</v>
